--- a/Tools/Excel/Datas/Item.xlsx
+++ b/Tools/Excel/Datas/Item.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -63,6 +63,9 @@
     <t>icon</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -96,91 +99,175 @@
     <t>道具-玫瑰</t>
   </si>
   <si>
-    <t>icon_200001</t>
+    <t>icon_item_200001</t>
   </si>
   <si>
     <t>道具-口红</t>
   </si>
   <si>
+    <t>icon_item_200002</t>
+  </si>
+  <si>
     <t>道具-钻戒</t>
   </si>
   <si>
+    <t>icon_item_200003</t>
+  </si>
+  <si>
     <t>道具-纲手（碎片）</t>
   </si>
   <si>
+    <t>icon_item_200004</t>
+  </si>
+  <si>
     <t>道具-项圈</t>
   </si>
   <si>
+    <t>icon_item_200005</t>
+  </si>
+  <si>
     <t>道具-项链</t>
   </si>
   <si>
+    <t>icon_item_200006</t>
+  </si>
+  <si>
     <t>道具-手表</t>
   </si>
   <si>
+    <t>icon_item_200007</t>
+  </si>
+  <si>
     <t>道具-巧克力</t>
   </si>
   <si>
+    <t>icon_item_200008</t>
+  </si>
+  <si>
     <t>道具-发饰</t>
   </si>
   <si>
+    <t>icon_item_200009</t>
+  </si>
+  <si>
     <t>道具-挎包</t>
   </si>
   <si>
+    <t>icon_item_200010</t>
+  </si>
+  <si>
     <t>角色2碎片</t>
   </si>
   <si>
+    <t>icon_item_200011</t>
+  </si>
+  <si>
     <t>角色3碎片</t>
   </si>
   <si>
+    <t>icon_item_200012</t>
+  </si>
+  <si>
     <t>角色4碎片</t>
   </si>
   <si>
+    <t>icon_item_200013</t>
+  </si>
+  <si>
     <t>角色5碎片</t>
   </si>
   <si>
+    <t>icon_item_200014</t>
+  </si>
+  <si>
     <t>角色6碎片</t>
   </si>
   <si>
+    <t>icon_item_200015</t>
+  </si>
+  <si>
     <t>角色7碎片</t>
   </si>
   <si>
+    <t>icon_item_200016</t>
+  </si>
+  <si>
     <t>角色8碎片</t>
   </si>
   <si>
+    <t>icon_item_200017</t>
+  </si>
+  <si>
     <t>角色9碎片</t>
   </si>
   <si>
+    <t>icon_item_200018</t>
+  </si>
+  <si>
     <t>角色10碎片</t>
   </si>
   <si>
+    <t>icon_item_200019</t>
+  </si>
+  <si>
     <t>角色11碎片</t>
   </si>
   <si>
+    <t>icon_item_200020</t>
+  </si>
+  <si>
     <t>棒棒糖</t>
   </si>
   <si>
+    <t>icon_item_200021</t>
+  </si>
+  <si>
     <t>炸弹</t>
   </si>
   <si>
+    <t>icon_item_200022</t>
+  </si>
+  <si>
     <t>交换道具</t>
   </si>
   <si>
+    <t>icon_item_200023</t>
+  </si>
+  <si>
     <t>巧克力球</t>
   </si>
   <si>
+    <t>icon_item_200024</t>
+  </si>
+  <si>
     <t>无限精力</t>
   </si>
   <si>
+    <t>icon_item_200025</t>
+  </si>
+  <si>
     <t>金币</t>
   </si>
   <si>
+    <t>icon_item_200026</t>
+  </si>
+  <si>
     <t>调教币</t>
   </si>
   <si>
+    <t>icon_item_200027</t>
+  </si>
+  <si>
     <t>精力</t>
   </si>
   <si>
+    <t>icon_item_200028</t>
+  </si>
+  <si>
     <t>充值货币</t>
+  </si>
+  <si>
+    <t>icon_item_200029</t>
   </si>
 </sst>
 </file>
@@ -193,7 +280,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,13 +298,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -686,52 +766,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,79 +820,79 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -833,7 +913,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1161,16 +1241,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="4"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.6283185840708" style="3" customWidth="1"/>
-    <col min="3" max="5" width="23.7522123893805" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="3" max="6" width="23.7522123893805" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13.9" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="13.9" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1186,8 +1266,11 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1195,462 +1278,559 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:5">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:5">
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="33.95" customHeight="1" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="33.95" customHeight="1" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
       <c r="B6" s="3">
         <v>200001</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="3">
         <v>200002</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
+        <v>19</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
       <c r="B8" s="3">
         <v>200003</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
       <c r="B9" s="3">
         <v>200004</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
+        <v>23</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="3">
         <v>200005</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
       <c r="B11" s="3">
         <v>200006</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
+        <v>27</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
       <c r="B12" s="3">
         <v>200007</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
+        <v>29</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
       <c r="B13" s="3">
         <v>200008</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
+        <v>31</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
       <c r="B14" s="3">
         <v>200009</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
+        <v>33</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
       <c r="B15" s="3">
         <v>200010</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
+        <v>35</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
       <c r="B16" s="3">
         <v>200011</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+        <v>37</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
       <c r="B17" s="3">
         <v>200012</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
+        <v>39</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="3">
         <v>200013</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <v>41</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" s="3">
         <v>200014</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
+        <v>43</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="3">
         <v>200015</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
+        <v>45</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
       <c r="B21" s="3">
         <v>200016</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
+        <v>47</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
       <c r="B22" s="3">
         <v>200017</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
+        <v>49</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
       <c r="B23" s="3">
         <v>200018</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
+        <v>51</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
       <c r="B24" s="3">
         <v>200019</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
+        <v>53</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
       <c r="B25" s="3">
         <v>200020</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
+        <v>55</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
       <c r="B26" s="3">
         <v>200021</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
+        <v>57</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="B27" s="3">
         <v>200022</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+        <v>59</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
       <c r="B28" s="3">
         <v>200023</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
+        <v>61</v>
+      </c>
+      <c r="F28" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
       <c r="B29" s="3">
         <v>200024</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
+        <v>63</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="3">
         <v>200025</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
+        <v>65</v>
+      </c>
+      <c r="F30" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="3">
         <v>200026</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
+        <v>67</v>
+      </c>
+      <c r="F31" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="3">
         <v>200027</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
+        <v>69</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
       <c r="B33" s="3">
         <v>200028</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
+        <v>71</v>
+      </c>
+      <c r="F33" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="3">
         <v>200029</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>16</v>
+        <v>73</v>
+      </c>
+      <c r="F34" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
